--- a/target/test-classes/TestData/Login.xlsx
+++ b/target/test-classes/TestData/Login.xlsx
@@ -5,17 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HIEN\AT\DWR\src\test\resources\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ROSY\TESTER\SeleniumJava\DWR\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1D0DB7-FBF7-4DBE-966B-A902F77B7166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185BCDE1-28CE-46C1-B990-857AE05BD4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3BB357F-4007-4027-BE32-E1BA3BF329DF}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{E3BB357F-4007-4027-BE32-E1BA3BF329DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="LoginFail" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,18 +26,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="20">
-  <si>
-    <t>TCS_NAME</t>
-  </si>
-  <si>
-    <t>EMAIL</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
   <si>
     <t>PASSWORD</t>
-  </si>
-  <si>
-    <t>admin@example.com</t>
   </si>
   <si>
     <t>USERNAME</t>
@@ -484,106 +474,106 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -617,37 +607,37 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -658,68 +648,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0998A7E7-0EBE-4D0D-A620-D2B5D40F6AFA}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>123456</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>123456</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{32CE229C-E53D-4848-8AD2-B108FBCB3C55}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{BB5A2047-D41B-4201-A9E4-ABBD24205CFF}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{74110265-D458-4EB5-B46D-DFC9391524B4}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{6EF02955-87DD-47DA-B4FC-29430CCDE802}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/target/test-classes/TestData/Login.xlsx
+++ b/target/test-classes/TestData/Login.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ROSY\TESTER\SeleniumJava\DWR\src\test\resources\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HIEN\AT\DWR2510\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185BCDE1-28CE-46C1-B990-857AE05BD4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD655E4A-F6E7-4B43-8D4B-DFCCAF9F4C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{E3BB357F-4007-4027-BE32-E1BA3BF329DF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3BB357F-4007-4027-BE32-E1BA3BF329DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>PASSWORD</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>G1_FLL</t>
+  </si>
+  <si>
+    <t>G1_CS</t>
+  </si>
+  <si>
+    <t>G2_CS</t>
+  </si>
+  <si>
+    <t>G3_CS</t>
   </si>
 </sst>
 </file>
@@ -465,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4A4787-DBDA-4195-958C-663C0E9C010A}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" customWidth="1"/>
@@ -573,6 +582,30 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -591,6 +624,9 @@
     <hyperlink ref="B11" r:id="rId10" xr:uid="{55159915-0BB7-4DD6-8BB2-5C3D4B2EDE1D}"/>
     <hyperlink ref="B12" r:id="rId11" xr:uid="{47AD3351-501F-4996-AB86-C1CCC00B6E9C}"/>
     <hyperlink ref="B13" r:id="rId12" xr:uid="{2158CBDC-7991-46E0-9C73-9810E3FE3B90}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{429177FC-0D12-4548-96FA-05BD0754B06A}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{0D307C8C-F0EF-458C-9565-AD47389A98F9}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{4C2FC755-7C4D-459E-AF67-45DE4135BC83}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/target/test-classes/TestData/Login.xlsx
+++ b/target/test-classes/TestData/Login.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HIEN\AT\DWR2510\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD655E4A-F6E7-4B43-8D4B-DFCCAF9F4C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B874839-B7AA-45A1-BCC1-7CB57BF4F47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3BB357F-4007-4027-BE32-E1BA3BF329DF}"/>
+    <workbookView xWindow="32700" yWindow="1290" windowWidth="21600" windowHeight="13215" xr2:uid="{E3BB357F-4007-4027-BE32-E1BA3BF329DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
   <si>
     <t>PASSWORD</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>G6_FL</t>
-  </si>
-  <si>
-    <t>G1_Cashier</t>
   </si>
   <si>
     <t>G2_Cashier</t>
@@ -474,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4A4787-DBDA-4195-958C-663C0E9C010A}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" customWidth="1"/>
@@ -579,7 +576,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>3</v>
@@ -598,14 +595,6 @@
         <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -618,15 +607,14 @@
     <hyperlink ref="B5" r:id="rId4" xr:uid="{1974CE6C-0792-4CCC-9CC3-8055DBE3C0E6}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{30204981-9670-4A4E-A3D2-BD4693783FBA}"/>
     <hyperlink ref="B7" r:id="rId6" xr:uid="{E9C8EFF8-A8D2-489E-B2E8-D095C2B1374A}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{6D179C92-2F6D-4531-808D-37647676006C}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{251AEE47-EC23-4D00-AB64-0FB41345BCBE}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{2BD16B96-41DD-4E02-9BDF-56C35C1052F1}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{55159915-0BB7-4DD6-8BB2-5C3D4B2EDE1D}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{47AD3351-501F-4996-AB86-C1CCC00B6E9C}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{2158CBDC-7991-46E0-9C73-9810E3FE3B90}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{429177FC-0D12-4548-96FA-05BD0754B06A}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{0D307C8C-F0EF-458C-9565-AD47389A98F9}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{4C2FC755-7C4D-459E-AF67-45DE4135BC83}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{251AEE47-EC23-4D00-AB64-0FB41345BCBE}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{2BD16B96-41DD-4E02-9BDF-56C35C1052F1}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{55159915-0BB7-4DD6-8BB2-5C3D4B2EDE1D}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{47AD3351-501F-4996-AB86-C1CCC00B6E9C}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{2158CBDC-7991-46E0-9C73-9810E3FE3B90}"/>
+    <hyperlink ref="B14" r:id="rId12" xr:uid="{0D307C8C-F0EF-458C-9565-AD47389A98F9}"/>
+    <hyperlink ref="B15" r:id="rId13" xr:uid="{4C2FC755-7C4D-459E-AF67-45DE4135BC83}"/>
+    <hyperlink ref="B13" r:id="rId14" xr:uid="{429177FC-0D12-4548-96FA-05BD0754B06A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -651,7 +639,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -662,7 +650,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">

--- a/target/test-classes/TestData/Login.xlsx
+++ b/target/test-classes/TestData/Login.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HIEN\AT\DWR2510\src\test\resources\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ROSY\TSO\AT\DWR2510\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B874839-B7AA-45A1-BCC1-7CB57BF4F47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B392C8ED-139F-4C27-BBB3-16CE85D18AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32700" yWindow="1290" windowWidth="21600" windowHeight="13215" xr2:uid="{E3BB357F-4007-4027-BE32-E1BA3BF329DF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3BB357F-4007-4027-BE32-E1BA3BF329DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
